--- a/Tools/excel2json/excel/SpawnDefine.xlsx
+++ b/Tools/excel2json/excel/SpawnDefine.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29" uniqueCount="20">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="18">
   <si>
     <t>ID</t>
   </si>
@@ -80,13 +80,7 @@
     <t>[0,0,0]</t>
   </si>
   <si>
-    <t>[153000,0,164212]</t>
-  </si>
-  <si>
-    <t>[268989,0,326212]</t>
-  </si>
-  <si>
-    <t>[260000,0,326212]</t>
+    <t>[155981,0,164212]</t>
   </si>
 </sst>
 </file>
@@ -1047,8 +1041,8 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:G7"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5" customHeight="1" outlineLevelRow="6" outlineLevelCol="6"/>
+  <dimension ref="A1:G5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5" customHeight="1" outlineLevelRow="4" outlineLevelCol="6"/>
   <cols>
     <col min="1" max="1" width="9" style="3"/>
     <col min="2" max="2" width="20.75" style="3" customWidth="1"/>
@@ -1149,7 +1143,7 @@
         <v>2</v>
       </c>
       <c r="G4" s="3">
-        <v>60</v>
+        <v>20</v>
       </c>
     </row>
     <row r="5" customHeight="1" spans="1:7">
@@ -1172,53 +1166,7 @@
         <v>4</v>
       </c>
       <c r="G5" s="3">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="6" customHeight="1" spans="1:7">
-      <c r="A6" s="3">
-        <v>2</v>
-      </c>
-      <c r="B6" s="3">
-        <v>2</v>
-      </c>
-      <c r="C6" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="D6" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="E6" s="3">
-        <v>1001</v>
-      </c>
-      <c r="F6" s="3">
-        <v>6</v>
-      </c>
-      <c r="G6" s="3">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="7" customHeight="1" spans="1:7">
-      <c r="A7" s="3">
-        <v>3</v>
-      </c>
-      <c r="B7" s="3">
-        <v>2</v>
-      </c>
-      <c r="C7" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="D7" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="E7" s="3">
-        <v>1001</v>
-      </c>
-      <c r="F7" s="3">
-        <v>8</v>
-      </c>
-      <c r="G7" s="3">
-        <v>60</v>
+        <v>20</v>
       </c>
     </row>
   </sheetData>

--- a/Tools/excel2json/excel/SpawnDefine.xlsx
+++ b/Tools/excel2json/excel/SpawnDefine.xlsx
@@ -74,13 +74,13 @@
     <t>刷怪周期(秒)</t>
   </si>
   <si>
-    <t>[153989,0,164212]</t>
+    <t>[310000,0,178000]</t>
   </si>
   <si>
     <t>[0,0,0]</t>
   </si>
   <si>
-    <t>[155981,0,164212]</t>
+    <t>[310000,0,178100]</t>
   </si>
 </sst>
 </file>

--- a/Tools/excel2json/excel/SpawnDefine.xlsx
+++ b/Tools/excel2json/excel/SpawnDefine.xlsx
@@ -1134,7 +1134,7 @@
         <v>0</v>
       </c>
       <c r="B4" s="3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C4" s="3" t="s">
         <v>15</v>
@@ -1157,7 +1157,7 @@
         <v>1</v>
       </c>
       <c r="B5" s="3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C5" s="3" t="s">
         <v>17</v>
@@ -1203,7 +1203,7 @@
         <v>3</v>
       </c>
       <c r="B7" s="3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C7" s="3" t="s">
         <v>19</v>
